--- a/data/templates/contract_anchor_db/智书合同字段-主播流程.xlsx
+++ b/data/templates/contract_anchor_db/智书合同字段-主播流程.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="字段模板" sheetId="1" r:id="rId1"/>
@@ -44,12 +44,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="182">
   <si>
     <t>contract_number（合同编码）</t>
   </si>
   <si>
     <t>contract_name（合同名称）</t>
+  </si>
+  <si>
+    <t>订单编号</t>
   </si>
   <si>
     <t>contractCategory(智书框架合同类型)</t>
@@ -1566,14 +1569,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AU1"/>
+  <dimension ref="A1:AV1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.2857142857143" customWidth="1"/>
-    <col min="2" max="47" width="34" customWidth="1"/>
+    <col min="2" max="48" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1" spans="1:47">
+    <row r="1" ht="60" customHeight="1" spans="1:48">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1628,7 +1631,7 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="2" t="s">
@@ -1649,7 +1652,7 @@
       <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
       <c r="AA1" s="1" t="s">
@@ -1682,13 +1685,13 @@
       <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AL1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>38</v>
       </c>
       <c r="AN1" s="1" t="s">
@@ -1697,7 +1700,7 @@
       <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="AQ1" s="2" t="s">
@@ -1706,43 +1709,46 @@
       <c r="AR1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E1048576">
       <formula1>DV_1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F1048576">
       <formula1>DV_2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:L1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M2:M1048576">
       <formula1>DV_3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P2:P1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q2:Q1048576">
       <formula1>DV_4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y2:Y1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z2:Z1048576">
       <formula1>DV_8</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z2:Z1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA2:AA1048576">
       <formula1>DV_5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AM2:AM1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AN2:AN1048576">
       <formula1>DV_6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AN2:AN1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AO2:AO1048576">
       <formula1>DV_7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AS2:AS1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AT2:AT1048576">
       <formula1>DV_9</formula1>
     </dataValidation>
   </dataValidations>
@@ -1759,498 +1765,498 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="G5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="G6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="G7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="G8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="G9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="G10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="G11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="G12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="G13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="G14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="G15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="G16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="7:9">
       <c r="G17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="7:9">
       <c r="G18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="7:9">
       <c r="H19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="7:9">
       <c r="H20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="7:9">
       <c r="H21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="7:9">
       <c r="H22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="7:9">
       <c r="H23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="7:9">
       <c r="H24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="7:9">
       <c r="H25" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="7:9">
       <c r="H26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I26" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="7:9">
       <c r="H27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="7:9">
       <c r="H28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="7:9">
       <c r="H29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="7:9">
       <c r="H30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="7:9">
       <c r="H31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="7:9">
       <c r="H32" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="8:8">
       <c r="H33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34" spans="8:8">
       <c r="H34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="8:8">
       <c r="H35" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="8:8">
       <c r="H36" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="8:8">
       <c r="H37" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" spans="8:8">
       <c r="H38" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="8:8">
       <c r="H39" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="8:8">
       <c r="H40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="8:8">
       <c r="H41" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="42" spans="8:8">
       <c r="H42" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="8:8">
       <c r="H43" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44" spans="8:8">
       <c r="H44" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="45" spans="8:8">
       <c r="H45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="8:8">
       <c r="H46" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" spans="8:8">
       <c r="H47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" spans="8:8">
       <c r="H48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="8:8">
       <c r="H49" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="50" spans="8:8">
       <c r="H50" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="8:8">
       <c r="H51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="8:8">
       <c r="H52" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="53" spans="8:8">
       <c r="H53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="8:8">
       <c r="H54" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="8:8">
       <c r="H55" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" spans="8:8">
       <c r="H56" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2273,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -2296,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2320,16 +2326,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/data/templates/contract_anchor_db/智书合同字段-主播流程.xlsx
+++ b/data/templates/contract_anchor_db/智书合同字段-主播流程.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="字段模板" sheetId="1" r:id="rId1"/>
@@ -44,12 +44,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="183">
   <si>
     <t>contract_number（合同编码）</t>
   </si>
   <si>
     <t>contract_name（合同名称）</t>
+  </si>
+  <si>
+    <t>合同状态</t>
   </si>
   <si>
     <t>订单编号</t>
@@ -602,7 +605,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -612,6 +615,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -767,7 +777,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -777,6 +787,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1097,70 +1113,67 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1175,79 +1188,88 @@
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1569,24 +1591,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AV1"/>
+  <dimension ref="A1:AW1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.2857142857143" customWidth="1"/>
-    <col min="2" max="48" width="34" customWidth="1"/>
+    <col min="2" max="49" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1" spans="1:48">
+    <row r="1" ht="60" customHeight="1" spans="1:49">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1634,28 +1656,28 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="4" t="s">
         <v>26</v>
       </c>
       <c r="AB1" s="1" t="s">
@@ -1688,13 +1710,13 @@
       <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" s="4" t="s">
         <v>39</v>
       </c>
       <c r="AO1" s="1" t="s">
@@ -1703,52 +1725,55 @@
       <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AS1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" s="4" t="s">
         <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F1048576">
       <formula1>DV_1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G1048576">
       <formula1>DV_2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M2:M1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N2:N1048576">
       <formula1>DV_3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q2:Q1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1048576">
       <formula1>DV_4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z2:Z1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA2:AA1048576">
       <formula1>DV_8</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA2:AA1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AB2:AB1048576">
       <formula1>DV_5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AN2:AN1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AO2:AO1048576">
       <formula1>DV_6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AO2:AO1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AP2:AP1048576">
       <formula1>DV_7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AT2:AT1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AU2:AU1048576">
       <formula1>DV_9</formula1>
     </dataValidation>
   </dataValidations>
@@ -1765,498 +1790,498 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="G5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="G6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="G7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="G8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="G9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="G10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="G11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="G12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="G13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="G14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="G15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="G16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="7:9">
       <c r="G17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="7:9">
       <c r="G18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="7:9">
       <c r="H19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="7:9">
       <c r="H20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="7:9">
       <c r="H21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="7:9">
       <c r="H22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="7:9">
       <c r="H23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="7:9">
       <c r="H24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="7:9">
       <c r="H25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="7:9">
       <c r="H26" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I26" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="7:9">
       <c r="H27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="7:9">
       <c r="H28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="7:9">
       <c r="H29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="7:9">
       <c r="H30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I30" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="7:9">
       <c r="H31" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="7:9">
       <c r="H32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33" spans="8:8">
       <c r="H33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="8:8">
       <c r="H34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="8:8">
       <c r="H35" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="8:8">
       <c r="H36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="8:8">
       <c r="H37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="8:8">
       <c r="H38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="8:8">
       <c r="H39" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="8:8">
       <c r="H40" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" spans="8:8">
       <c r="H41" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" spans="8:8">
       <c r="H42" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43" spans="8:8">
       <c r="H43" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="8:8">
       <c r="H44" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="8:8">
       <c r="H45" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="8:8">
       <c r="H46" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" spans="8:8">
       <c r="H47" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="8:8">
       <c r="H48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="49" spans="8:8">
       <c r="H49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" spans="8:8">
       <c r="H50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="8:8">
       <c r="H51" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="8:8">
       <c r="H52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" spans="8:8">
       <c r="H53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="8:8">
       <c r="H54" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="8:8">
       <c r="H55" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="56" spans="8:8">
       <c r="H56" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -2279,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2302,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2326,16 +2351,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/data/templates/contract_anchor_db/智书合同字段-主播流程.xlsx
+++ b/data/templates/contract_anchor_db/智书合同字段-主播流程.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="184">
   <si>
     <t>contract_number（合同编码）</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>remark（合同说明）</t>
+  </si>
+  <si>
+    <t>custom_1001_948719050bfe402ab083c98e52fa71b2（合同执行人）飞书user_id</t>
   </si>
   <si>
     <t>custom_15_78cf503c57194e4fb8ad03ded1c4ad60（打印模式）</t>
@@ -1591,14 +1594,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AW1"/>
+  <dimension ref="A1:AX1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.2857142857143" customWidth="1"/>
-    <col min="2" max="49" width="34" customWidth="1"/>
+    <col min="2" max="50" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1" spans="1:49">
+    <row r="1" ht="60" customHeight="1" spans="1:50">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1659,7 +1662,7 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="4" t="s">
@@ -1680,7 +1683,7 @@
       <c r="AA1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
@@ -1713,13 +1716,13 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="4" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
       <c r="AN1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="4" t="s">
         <v>40</v>
       </c>
       <c r="AP1" s="1" t="s">
@@ -1728,7 +1731,7 @@
       <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="4" t="s">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="AS1" s="4" t="s">
@@ -1737,14 +1740,17 @@
       <c r="AT1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="4" t="s">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" s="4" t="s">
         <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1758,22 +1764,22 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N2:N1048576">
       <formula1>DV_3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1048576 S2:S1048576">
       <formula1>DV_4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA2:AA1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AB2:AB1048576">
       <formula1>DV_8</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AB2:AB1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AC2:AC1048576">
       <formula1>DV_5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AO2:AO1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AP2:AP1048576">
       <formula1>DV_6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AP2:AP1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AQ2:AQ1048576">
       <formula1>DV_7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AU2:AU1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AV2:AV1048576">
       <formula1>DV_9</formula1>
     </dataValidation>
   </dataValidations>
@@ -1790,498 +1796,498 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="G5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="G6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="G7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="G8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="G9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="G10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="G11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="G12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="G13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="G14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="G15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="G16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="7:9">
       <c r="G17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="7:9">
       <c r="G18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="7:9">
       <c r="H19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="7:9">
       <c r="H20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="7:9">
       <c r="H21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="7:9">
       <c r="H22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="7:9">
       <c r="H23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="7:9">
       <c r="H24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="7:9">
       <c r="H25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="7:9">
       <c r="H26" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I26" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="7:9">
       <c r="H27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="7:9">
       <c r="H28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="7:9">
       <c r="H29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="7:9">
       <c r="H30" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I30" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="7:9">
       <c r="H31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="7:9">
       <c r="H32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="8:8">
       <c r="H33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="8:8">
       <c r="H34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="8:8">
       <c r="H35" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="8:8">
       <c r="H36" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="8:8">
       <c r="H37" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="8:8">
       <c r="H38" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="8:8">
       <c r="H39" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="8:8">
       <c r="H40" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="8:8">
       <c r="H41" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="8:8">
       <c r="H42" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="43" spans="8:8">
       <c r="H43" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="8:8">
       <c r="H44" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" spans="8:8">
       <c r="H45" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" spans="8:8">
       <c r="H46" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="8:8">
       <c r="H47" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" spans="8:8">
       <c r="H48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="8:8">
       <c r="H49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="8:8">
       <c r="H50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" spans="8:8">
       <c r="H51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="8:8">
       <c r="H52" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="53" spans="8:8">
       <c r="H53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="8:8">
       <c r="H54" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55" spans="8:8">
       <c r="H55" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="8:8">
       <c r="H56" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2304,7 +2310,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2327,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -2351,16 +2357,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/data/templates/contract_anchor_db/智书合同字段-主播流程.xlsx
+++ b/data/templates/contract_anchor_db/智书合同字段-主播流程.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="186">
   <si>
     <t>contract_number（合同编码）</t>
   </si>
@@ -97,16 +97,22 @@
     <t>remark（合同说明）</t>
   </si>
   <si>
+    <t>custom_15_78cf503c57194e4fb8ad03ded1c4ad60（打印模式）</t>
+  </si>
+  <si>
+    <t>custom_10_9a2a0e99771346c98bfb6cfb893e1bee（签署日期）</t>
+  </si>
+  <si>
+    <t>custom_1001_948719050bfe402ab083c98e52fa71b2（合同执行人）</t>
+  </si>
+  <si>
     <t>custom_1001_948719050bfe402ab083c98e52fa71b2（合同执行人）飞书user_id</t>
   </si>
   <si>
-    <t>custom_15_78cf503c57194e4fb8ad03ded1c4ad60（打印模式）</t>
-  </si>
-  <si>
-    <t>custom_10_9a2a0e99771346c98bfb6cfb893e1bee（签署日期）</t>
-  </si>
-  <si>
-    <t>custom_1001_948719050bfe402ab083c98e52fa71b2（合同执行人）</t>
+    <t>合同创建人</t>
+  </si>
+  <si>
+    <t>合同创建人user_id</t>
   </si>
   <si>
     <t>custom_1024_61820798c0f348658d8daa64f8b2aef9（主播卡片）</t>
@@ -1594,14 +1600,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AX1"/>
+  <dimension ref="A1:AZ1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.2857142857143" customWidth="1"/>
-    <col min="2" max="50" width="34" customWidth="1"/>
+    <col min="2" max="52" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1" spans="1:50">
+    <row r="1" ht="60" customHeight="1" spans="1:52">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1665,10 +1671,10 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="4" t="s">
@@ -1686,10 +1692,10 @@
       <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="1" t="s">
@@ -1719,31 +1725,31 @@
       <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="4" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="4" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="4" t="s">
         <v>42</v>
       </c>
       <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="4" t="s">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="4" t="s">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
       <c r="AU1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" s="4" t="s">
         <v>47</v>
       </c>
       <c r="AW1" s="4" t="s">
@@ -1751,6 +1757,12 @@
       </c>
       <c r="AX1" s="1" t="s">
         <v>49</v>
+      </c>
+      <c r="AY1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1764,22 +1776,22 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N2:N1048576">
       <formula1>DV_3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1048576 S2:S1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1048576">
       <formula1>DV_4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AB2:AB1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AD2:AD1048576">
       <formula1>DV_8</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AC2:AC1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AE2:AE1048576">
       <formula1>DV_5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AP2:AP1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AR2:AR1048576">
       <formula1>DV_6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AQ2:AQ1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AS2:AS1048576">
       <formula1>DV_7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AV2:AV1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AX2:AX1048576">
       <formula1>DV_9</formula1>
     </dataValidation>
   </dataValidations>
@@ -1796,498 +1808,498 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="G5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="G6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="G7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="G8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="G9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="G10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="G11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="G12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="G13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="G14" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="G15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="G16" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H16" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="7:9">
       <c r="G17" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H17" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I17" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="7:9">
       <c r="G18" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H18" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I18" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="7:9">
       <c r="H19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I19" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="7:9">
       <c r="H20" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="7:9">
       <c r="H21" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I21" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="7:9">
       <c r="H22" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I22" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="7:9">
       <c r="H23" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I23" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="7:9">
       <c r="H24" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I24" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="7:9">
       <c r="H25" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="7:9">
       <c r="H26" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I26" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="7:9">
       <c r="H27" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I27" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="7:9">
       <c r="H28" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I28" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="7:9">
       <c r="H29" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I29" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="7:9">
       <c r="H30" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="7:9">
       <c r="H31" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="7:9">
       <c r="H32" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="8:8">
       <c r="H33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="8:8">
       <c r="H34" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="8:8">
       <c r="H35" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36" spans="8:8">
       <c r="H36" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" spans="8:8">
       <c r="H37" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="8:8">
       <c r="H38" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="8:8">
       <c r="H39" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="40" spans="8:8">
       <c r="H40" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="8:8">
       <c r="H41" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="8:8">
       <c r="H42" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="8:8">
       <c r="H43" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="8:8">
       <c r="H44" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="8:8">
       <c r="H45" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="46" spans="8:8">
       <c r="H46" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="8:8">
       <c r="H47" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="8:8">
       <c r="H48" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="8:8">
       <c r="H49" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="8:8">
       <c r="H50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51" spans="8:8">
       <c r="H51" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" spans="8:8">
       <c r="H52" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53" spans="8:8">
       <c r="H53" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="54" spans="8:8">
       <c r="H54" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55" spans="8:8">
       <c r="H55" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="56" spans="8:8">
       <c r="H56" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -2310,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2333,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2357,16 +2369,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/data/templates/contract_anchor_db/智书合同字段-主播流程.xlsx
+++ b/data/templates/contract_anchor_db/智书合同字段-主播流程.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="187">
   <si>
     <t>contract_number（合同编码）</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>合同创建人user_id</t>
+  </si>
+  <si>
+    <t>申请人状态</t>
   </si>
   <si>
     <t>custom_1024_61820798c0f348658d8daa64f8b2aef9（主播卡片）</t>
@@ -1600,14 +1603,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AZ1"/>
+  <dimension ref="A1:BA1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.2857142857143" customWidth="1"/>
-    <col min="2" max="52" width="34" customWidth="1"/>
+    <col min="2" max="53" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1" spans="1:52">
+    <row r="1" ht="60" customHeight="1" spans="1:53">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1677,7 +1680,7 @@
       <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
       <c r="Y1" s="4" t="s">
@@ -1698,7 +1701,7 @@
       <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="4" t="s">
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
@@ -1731,13 +1734,13 @@
       <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="4" t="s">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="AQ1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" s="4" t="s">
         <v>43</v>
       </c>
       <c r="AS1" s="1" t="s">
@@ -1746,7 +1749,7 @@
       <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="4" t="s">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
       <c r="AV1" s="4" t="s">
@@ -1755,14 +1758,17 @@
       <c r="AW1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="4" t="s">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" s="4" t="s">
         <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1779,19 +1785,19 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1048576">
       <formula1>DV_4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AD2:AD1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AE2:AE1048576">
       <formula1>DV_8</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AE2:AE1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF2:AF1048576">
       <formula1>DV_5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AR2:AR1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AS2:AS1048576">
       <formula1>DV_6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AS2:AS1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AT2:AT1048576">
       <formula1>DV_7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AX2:AX1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AY2:AY1048576">
       <formula1>DV_9</formula1>
     </dataValidation>
   </dataValidations>
@@ -1808,498 +1814,498 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="G5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="G6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="G7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="G8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="G9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="G10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="G11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="G12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="G13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="G14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="G15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="G16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="7:9">
       <c r="G17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="7:9">
       <c r="G18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="7:9">
       <c r="H19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="7:9">
       <c r="H20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="7:9">
       <c r="H21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="7:9">
       <c r="H22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="7:9">
       <c r="H23" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="7:9">
       <c r="H24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="7:9">
       <c r="H25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="7:9">
       <c r="H26" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="7:9">
       <c r="H27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="7:9">
       <c r="H28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="7:9">
       <c r="H29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="7:9">
       <c r="H30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="7:9">
       <c r="H31" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="7:9">
       <c r="H32" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="8:8">
       <c r="H33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="8:8">
       <c r="H34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35" spans="8:8">
       <c r="H35" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="8:8">
       <c r="H36" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="37" spans="8:8">
       <c r="H37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="8:8">
       <c r="H38" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="8:8">
       <c r="H39" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40" spans="8:8">
       <c r="H40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="8:8">
       <c r="H41" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" spans="8:8">
       <c r="H42" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="8:8">
       <c r="H43" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="8:8">
       <c r="H44" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="8:8">
       <c r="H45" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="8:8">
       <c r="H46" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="8:8">
       <c r="H47" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="8:8">
       <c r="H48" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="8:8">
       <c r="H49" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="8:8">
       <c r="H50" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="8:8">
       <c r="H51" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52" spans="8:8">
       <c r="H52" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="53" spans="8:8">
       <c r="H53" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="8:8">
       <c r="H54" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="55" spans="8:8">
       <c r="H55" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="56" spans="8:8">
       <c r="H56" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2322,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2345,7 +2351,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -2369,16 +2375,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/data/templates/contract_anchor_db/智书合同字段-主播流程.xlsx
+++ b/data/templates/contract_anchor_db/智书合同字段-主播流程.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="26505" windowHeight="17055"/>
   </bookViews>
   <sheets>
     <sheet name="字段模板" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,8 @@
     <sheet name="对方信息" sheetId="3" r:id="rId3"/>
     <sheet name="我方信息" sheetId="5" r:id="rId4"/>
     <sheet name="费用明细" sheetId="8" r:id="rId5"/>
+    <sheet name="合同附件" sheetId="10" r:id="rId6"/>
+    <sheet name="其他附件" sheetId="11" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="DV_1">选项!$A$1:$A$4</definedName>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="188">
   <si>
     <t>contract_number（合同编码）</t>
   </si>
@@ -52,6 +54,9 @@
     <t>contract_name（合同名称）</t>
   </si>
   <si>
+    <t>合同审批状态</t>
+  </si>
+  <si>
     <t>合同状态</t>
   </si>
   <si>
@@ -115,7 +120,7 @@
     <t>合同创建人user_id</t>
   </si>
   <si>
-    <t>申请人状态</t>
+    <t>合同创建人状态</t>
   </si>
   <si>
     <t>custom_1024_61820798c0f348658d8daa64f8b2aef9（主播卡片）</t>
@@ -617,9 +622,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -789,7 +801,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -804,6 +816,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1001,12 +1019,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1125,70 +1158,67 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1203,85 +1233,94 @@
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1603,201 +1642,204 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BA1"/>
+  <dimension ref="A1:BB1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.2857142857143" customWidth="1"/>
-    <col min="2" max="53" width="34" customWidth="1"/>
+    <col min="2" max="54" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1" spans="1:53">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="60" customHeight="1" spans="1:54">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
       <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AA1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AB1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AC1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AD1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="4" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="4" t="s">
+      <c r="AR1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="4" t="s">
+      <c r="AV1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="4" t="s">
+      <c r="AW1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="4" t="s">
+      <c r="AX1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="4" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" s="6" t="s">
         <v>52</v>
+      </c>
+      <c r="BB1" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G1048576">
       <formula1>DV_1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H1048576">
       <formula1>DV_2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N2:N1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O2:O1048576">
       <formula1>DV_3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="S2:S1048576">
       <formula1>DV_4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AE2:AE1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF2:AF1048576">
       <formula1>DV_8</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF2:AF1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AG2:AG1048576">
       <formula1>DV_5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AS2:AS1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AT2:AT1048576">
       <formula1>DV_6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AT2:AT1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AU2:AU1048576">
       <formula1>DV_7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AY2:AY1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AZ2:AZ1048576">
       <formula1>DV_9</formula1>
     </dataValidation>
   </dataValidations>
@@ -1814,498 +1856,498 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="G5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="G6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="G7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="G8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="G9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="G10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="G11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="G12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="G13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="G14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="G15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="G16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="7:9">
       <c r="G17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="7:9">
       <c r="G18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="7:9">
       <c r="H19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="7:9">
       <c r="H20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="7:9">
       <c r="H21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="7:9">
       <c r="H22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="7:9">
       <c r="H23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="7:9">
       <c r="H24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="7:9">
       <c r="H25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="7:9">
       <c r="H26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="7:9">
       <c r="H27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="7:9">
       <c r="H28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="7:9">
       <c r="H29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="7:9">
       <c r="H30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I30" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="7:9">
       <c r="H31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="7:9">
       <c r="H32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="8:8">
       <c r="H33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34" spans="8:8">
       <c r="H34" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="8:8">
       <c r="H35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="36" spans="8:8">
       <c r="H36" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="8:8">
       <c r="H37" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="8:8">
       <c r="H38" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="8:8">
       <c r="H39" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="8:8">
       <c r="H40" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="8:8">
       <c r="H41" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="8:8">
       <c r="H42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="8:8">
       <c r="H43" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="44" spans="8:8">
       <c r="H44" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="8:8">
       <c r="H45" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="8:8">
       <c r="H46" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="8:8">
       <c r="H47" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="8:8">
       <c r="H48" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="8:8">
       <c r="H49" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" spans="8:8">
       <c r="H50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="8:8">
       <c r="H51" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" spans="8:8">
       <c r="H52" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" spans="8:8">
       <c r="H53" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54" spans="8:8">
       <c r="H54" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" spans="8:8">
       <c r="H55" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56" spans="8:8">
       <c r="H56" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2324,11 +2366,11 @@
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>181</v>
+      <c r="B1" s="3" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -2347,11 +2389,11 @@
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>182</v>
+      <c r="B1" s="3" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -2371,20 +2413,20 @@
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>186</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -2396,4 +2438,52 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="28.8571428571429" customWidth="1"/>
+    <col min="2" max="2" width="28.4285714285714" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.5" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="29.5714285714286" customWidth="1"/>
+    <col min="2" max="2" width="35.1428571428571" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="63" customHeight="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/data/templates/contract_anchor_db/智书合同字段-主播流程.xlsx
+++ b/data/templates/contract_anchor_db/智书合同字段-主播流程.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26505" windowHeight="17055"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="字段模板" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="187">
   <si>
     <t>contract_number（合同编码）</t>
   </si>
@@ -54,13 +54,10 @@
     <t>contract_name（合同名称）</t>
   </si>
   <si>
-    <t>合同审批状态</t>
+    <t>泛微合同状态</t>
   </si>
   <si>
     <t>合同状态</t>
-  </si>
-  <si>
-    <t>订单编号</t>
   </si>
   <si>
     <t>contractCategory(智书框架合同类型)</t>
@@ -622,7 +619,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -639,13 +636,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1158,152 +1148,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1315,9 +1305,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1642,14 +1629,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BB1"/>
+  <dimension ref="A1:BA1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.2857142857143" customWidth="1"/>
-    <col min="2" max="54" width="34" customWidth="1"/>
+    <col min="2" max="53" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1" spans="1:54">
+    <row r="1" ht="60" customHeight="1" spans="1:53">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1662,7 +1649,7 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -1713,7 +1700,7 @@
       <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="4" t="s">
@@ -1722,28 +1709,28 @@
       <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Z1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AA1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AB1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AC1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AD1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AE1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="3" t="s">
@@ -1776,13 +1763,13 @@
       <c r="AP1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AQ1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AR1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AS1" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AT1" s="3" t="s">
@@ -1791,55 +1778,52 @@
       <c r="AU1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AV1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AW1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AX1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="AY1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="AZ1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BA1" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="BB1" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F1048576">
       <formula1>DV_1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G1048576">
       <formula1>DV_2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O2:O1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N2:N1048576">
       <formula1>DV_3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="S2:S1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1048576">
       <formula1>DV_4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF2:AF1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AE2:AE1048576">
       <formula1>DV_8</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AG2:AG1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF2:AF1048576">
       <formula1>DV_5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AT2:AT1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AS2:AS1048576">
       <formula1>DV_6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AU2:AU1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AT2:AT1048576">
       <formula1>DV_7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AZ2:AZ1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AY2:AY1048576">
       <formula1>DV_9</formula1>
     </dataValidation>
   </dataValidations>
@@ -1856,498 +1840,498 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" t="s">
         <v>54</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>55</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>56</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>57</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>58</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>59</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>60</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>61</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>62</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>63</v>
-      </c>
-      <c r="K1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" t="s">
         <v>65</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>67</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>68</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>69</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>70</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>71</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>72</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>73</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>74</v>
-      </c>
-      <c r="K2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" t="s">
         <v>76</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
         <v>77</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>78</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>79</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>80</v>
-      </c>
-      <c r="J3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" t="s">
         <v>82</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>83</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>84</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>85</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>86</v>
-      </c>
-      <c r="J4" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="G5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" t="s">
         <v>88</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>89</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>90</v>
-      </c>
-      <c r="J5" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="G6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" t="s">
         <v>92</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>93</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>94</v>
-      </c>
-      <c r="J6" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="G7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H7" t="s">
         <v>96</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>97</v>
-      </c>
-      <c r="I7" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="G8" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8" t="s">
         <v>99</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>100</v>
-      </c>
-      <c r="I8" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="G9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" t="s">
         <v>102</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>103</v>
-      </c>
-      <c r="I9" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="G10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" t="s">
         <v>105</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>106</v>
-      </c>
-      <c r="I10" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="G11" t="s">
+        <v>107</v>
+      </c>
+      <c r="H11" t="s">
         <v>108</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>109</v>
-      </c>
-      <c r="I11" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="G12" t="s">
+        <v>110</v>
+      </c>
+      <c r="H12" t="s">
         <v>111</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>112</v>
-      </c>
-      <c r="I12" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="G13" t="s">
+        <v>113</v>
+      </c>
+      <c r="H13" t="s">
         <v>114</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>115</v>
-      </c>
-      <c r="I13" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="G14" t="s">
+        <v>116</v>
+      </c>
+      <c r="H14" t="s">
         <v>117</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>118</v>
-      </c>
-      <c r="I14" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="G15" t="s">
+        <v>119</v>
+      </c>
+      <c r="H15" t="s">
         <v>120</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>121</v>
-      </c>
-      <c r="I15" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="G16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H16" t="s">
         <v>123</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>124</v>
-      </c>
-      <c r="I16" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="17" spans="7:9">
       <c r="G17" t="s">
+        <v>125</v>
+      </c>
+      <c r="H17" t="s">
         <v>126</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>127</v>
-      </c>
-      <c r="I17" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="18" spans="7:9">
       <c r="G18" t="s">
+        <v>128</v>
+      </c>
+      <c r="H18" t="s">
         <v>129</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>130</v>
-      </c>
-      <c r="I18" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="19" spans="7:9">
       <c r="H19" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" t="s">
         <v>132</v>
-      </c>
-      <c r="I19" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="20" spans="7:9">
       <c r="H20" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" t="s">
         <v>134</v>
-      </c>
-      <c r="I20" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="21" spans="7:9">
       <c r="H21" t="s">
+        <v>135</v>
+      </c>
+      <c r="I21" t="s">
         <v>136</v>
-      </c>
-      <c r="I21" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="22" spans="7:9">
       <c r="H22" t="s">
+        <v>137</v>
+      </c>
+      <c r="I22" t="s">
         <v>138</v>
-      </c>
-      <c r="I22" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="23" spans="7:9">
       <c r="H23" t="s">
+        <v>139</v>
+      </c>
+      <c r="I23" t="s">
         <v>140</v>
-      </c>
-      <c r="I23" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="24" spans="7:9">
       <c r="H24" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" t="s">
         <v>142</v>
-      </c>
-      <c r="I24" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="25" spans="7:9">
       <c r="H25" t="s">
+        <v>143</v>
+      </c>
+      <c r="I25" t="s">
         <v>144</v>
-      </c>
-      <c r="I25" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="26" spans="7:9">
       <c r="H26" t="s">
+        <v>145</v>
+      </c>
+      <c r="I26" t="s">
         <v>146</v>
-      </c>
-      <c r="I26" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="27" spans="7:9">
       <c r="H27" t="s">
+        <v>147</v>
+      </c>
+      <c r="I27" t="s">
         <v>148</v>
-      </c>
-      <c r="I27" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="28" spans="7:9">
       <c r="H28" t="s">
+        <v>149</v>
+      </c>
+      <c r="I28" t="s">
         <v>150</v>
-      </c>
-      <c r="I28" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="29" spans="7:9">
       <c r="H29" t="s">
+        <v>151</v>
+      </c>
+      <c r="I29" t="s">
         <v>152</v>
-      </c>
-      <c r="I29" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="30" spans="7:9">
       <c r="H30" t="s">
+        <v>153</v>
+      </c>
+      <c r="I30" t="s">
         <v>154</v>
-      </c>
-      <c r="I30" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="31" spans="7:9">
       <c r="H31" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="7:9">
       <c r="H32" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="8:8">
       <c r="H33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="8:8">
       <c r="H34" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35" spans="8:8">
       <c r="H35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="8:8">
       <c r="H36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="37" spans="8:8">
       <c r="H37" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="8:8">
       <c r="H38" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="8:8">
       <c r="H39" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40" spans="8:8">
       <c r="H40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="8:8">
       <c r="H41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" spans="8:8">
       <c r="H42" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="8:8">
       <c r="H43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="8:8">
       <c r="H44" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="8:8">
       <c r="H45" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="8:8">
       <c r="H46" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="8:8">
       <c r="H47" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="8:8">
       <c r="H48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="8:8">
       <c r="H49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="8:8">
       <c r="H50" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="8:8">
       <c r="H51" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52" spans="8:8">
       <c r="H52" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="53" spans="8:8">
       <c r="H53" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="8:8">
       <c r="H54" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="55" spans="8:8">
       <c r="H55" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="56" spans="8:8">
       <c r="H56" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2370,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2393,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -2417,16 +2401,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -2455,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2479,7 +2463,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
